--- a/scored_applicants.xlsx
+++ b/scored_applicants.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,100 +429,105 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>How much experience do you have working with youth? (e.g., tutoring, mentoring, childcare, coaching, etc.)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>How much leadership experience do you have? (volunteering, clubs, sports, work experience, etc.)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Which of the following subjects have you taken or are currently taking? (Check all that apply)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>What technical skills do you have? (Check all that apply)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Have you previously been a volunteer with UWaterloo Engineering Outreach Summer Camps?</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Have you previously been a camper at UWaterloo Engineering Outreach Summer Camps?</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>How much experience do you have working with youth? (e.g., tutoring, mentoring, childcare, coaching, etc.) (score)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>How much leadership experience do you have? (volunteering, clubs, sports, work experience, etc.) (score)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Which of the following subjects have you taken or are currently taking? (Check all that apply) (score)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>What technical skills do you have? (Check all that apply) (score)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Have you previously been a volunteer with UWaterloo Engineering Outreach Summer Camps? (score)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Have you previously been a camper at UWaterloo Engineering Outreach Summer Camps? (score)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 1</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 2</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 4</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 5</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 6</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Please enter your weekly availability below. Disclaimer: This information is used for scheduling purposes only. Indicating availability does not guarantee selection as a volunteer or assignment to specific dates or shifts. - Week 7</t>
         </is>
@@ -539,7 +544,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -549,53 +554,53 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Math,Science,Chemistry,Physics</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Graphic Design,Video Editing</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>13</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am not available</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -605,20 +610,25 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
         </is>
@@ -635,7 +645,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -645,63 +655,63 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Programming,Math</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Coding,Robotics,3D Modeling</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
       <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -711,10 +721,15 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -731,68 +746,68 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>1-9 hours</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20+ hours</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Math,Robotics,Science,Physics,Chemistry,Programming</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Coding,Robotics</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
       <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>I am available this week</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -802,7 +817,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -811,6 +826,11 @@
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -827,7 +847,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -837,27 +857,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Science,Biology,Programmimg,Robotics</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Graphic Design,Coding,Robotics</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
@@ -868,27 +890,25 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>I am available this week</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -898,7 +918,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -907,6 +927,11 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -923,7 +948,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -933,76 +958,81 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Coding,Robotics</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -1019,7 +1049,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1029,50 +1059,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Programming </t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">Coding  </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
@@ -1080,7 +1110,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1090,7 +1120,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1099,6 +1129,11 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -1115,7 +1150,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1125,76 +1160,81 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
         <v>2</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>11</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
         </is>
@@ -1211,7 +1251,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1221,27 +1261,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Math,Robotics,Science</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
       <c r="J9" t="n">
         <v>3</v>
       </c>
@@ -1249,40 +1291,38 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>11</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1291,6 +1331,11 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
@@ -1307,7 +1352,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1317,50 +1362,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
         <v>2</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>10</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>I am available this week</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>I am available this week</t>
@@ -1368,12 +1413,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1387,6 +1432,11 @@
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -1403,7 +1453,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1413,76 +1463,81 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Programming,Robotics</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Coding,Robotics</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>10</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>I am available and prefer this week</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
@@ -1499,7 +1554,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1509,50 +1564,50 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>None of the Options</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
       <c r="J12" t="n">
         <v>3</v>
       </c>
       <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>10</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>I am available this week</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>I am available this week</t>
@@ -1579,6 +1634,11 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>I am available this week</t>
         </is>
@@ -1597,65 +1657,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Grade 10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>10-20 hours</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>10-20 hours</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Math,Programming,Chemistry,Physics,Biology</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>10</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>I am not available</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>I am available and prefer this week</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
@@ -1663,7 +1723,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1677,6 +1737,11 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
         </is>
@@ -1693,7 +1758,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20+ hours</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1703,50 +1768,50 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>20+ hours</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Science,Math</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>None of the Options</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>10</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>I am available this week</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>I am available this week</t>
@@ -1754,12 +1819,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>I am available and prefer this week</t>
+          <t>I am available this week</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>I am available this week</t>
+          <t>I am available and prefer this week</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1773,6 +1838,11 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>I am available this week</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>I am available and prefer this week</t>
         </is>

--- a/scored_applicants.xlsx
+++ b/scored_applicants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicol\Documents\Shiftly\capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C311F66-E90F-4A1E-9AC5-728AAB757F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DED74A0-4C89-44FF-AF52-3EDA2BDA8514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,11 +276,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,7 +661,7 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>57</v>
       </c>
       <c r="B2" t="s">
@@ -729,7 +732,7 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>28</v>
       </c>
       <c r="B3" t="s">
@@ -800,7 +803,7 @@
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>66</v>
       </c>
       <c r="B4" t="s">
@@ -871,7 +874,7 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>77</v>
       </c>
       <c r="B5" t="s">
@@ -942,7 +945,7 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>50</v>
       </c>
       <c r="B6" t="s">
@@ -1013,7 +1016,7 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>15</v>
       </c>
       <c r="B7" t="s">
@@ -1084,7 +1087,7 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>96</v>
       </c>
       <c r="B8" t="s">
@@ -1155,7 +1158,7 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>92</v>
       </c>
       <c r="B9" t="s">
@@ -1226,7 +1229,7 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>59</v>
       </c>
       <c r="B10" t="s">
@@ -1297,7 +1300,7 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="A11" s="4">
         <v>64</v>
       </c>
       <c r="B11" t="s">
@@ -1368,7 +1371,7 @@
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="A12" s="4">
         <v>12</v>
       </c>
       <c r="B12" t="s">
@@ -1439,7 +1442,7 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B13" t="s">
@@ -1510,7 +1513,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="A14" s="4">
         <v>70</v>
       </c>
       <c r="B14" t="s">
